--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2024_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2024_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:39</t>
+    <t xml:space="preserve">2026-09-09 22:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2024_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2024_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:26</t>
+    <t xml:space="preserve">2026-09-12 19:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2024_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2024_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:42</t>
+    <t xml:space="preserve">2026-09-24 00:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2024_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2024_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:20</t>
+    <t xml:space="preserve">2026-09-27 22:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2024_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2024_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:09</t>
+    <t xml:space="preserve">2026-09-29 11:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -493,7 +493,7 @@
         <v>2024</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>39.93</v>
+        <v>399.31</v>
       </c>
     </row>
     <row r="3">
@@ -510,7 +510,7 @@
         <v>2024</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>29.83</v>
+        <v>298.34</v>
       </c>
     </row>
     <row r="4">
@@ -527,7 +527,7 @@
         <v>2024</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>23.7</v>
+        <v>237.01</v>
       </c>
     </row>
     <row r="5">
@@ -544,7 +544,7 @@
         <v>2024</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>6.67</v>
+        <v>66.71</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2024_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2024_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 11:04</t>
+    <t xml:space="preserve">2026-10-01 19:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -75,7 +75,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2024_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2024_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 19:28</t>
+    <t xml:space="preserve">2026-10-02 13:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2024_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2024_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:11</t>
+    <t xml:space="preserve">2026-10-05 07:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
